--- a/output/yearly_population_iteration_12_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_12_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6590</v>
+        <v>6972</v>
       </c>
       <c r="C2" t="n">
-        <v>12402</v>
+        <v>8171</v>
       </c>
       <c r="D2" t="n">
-        <v>21779</v>
+        <v>27652</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4380</v>
+        <v>3394</v>
       </c>
       <c r="C3" t="n">
-        <v>5891</v>
+        <v>5070</v>
       </c>
       <c r="D3" t="n">
-        <v>16676</v>
+        <v>15027</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3395</v>
+        <v>2711</v>
       </c>
       <c r="C4" t="n">
-        <v>4519</v>
+        <v>3995</v>
       </c>
       <c r="D4" t="n">
-        <v>9201</v>
+        <v>6901</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2206</v>
+        <v>1906</v>
       </c>
       <c r="C5" t="n">
-        <v>3664</v>
+        <v>3447</v>
       </c>
       <c r="D5" t="n">
-        <v>3439</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1204</v>
+        <v>1124</v>
       </c>
       <c r="C6" t="n">
-        <v>2338</v>
+        <v>2173</v>
       </c>
       <c r="D6" t="n">
-        <v>1285</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>563</v>
+        <v>536</v>
       </c>
       <c r="C7" t="n">
-        <v>1420</v>
+        <v>1221</v>
       </c>
       <c r="D7" t="n">
-        <v>672</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="C8" t="n">
-        <v>738</v>
+        <v>535</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>339</v>
+        <v>264</v>
       </c>
       <c r="D9" t="n">
         <v>310</v>
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8693</v>
+        <v>7490</v>
       </c>
       <c r="C2" t="n">
-        <v>10928</v>
+        <v>13041</v>
       </c>
       <c r="D2" t="n">
-        <v>30134</v>
+        <v>23207</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4378</v>
+        <v>4073</v>
       </c>
       <c r="C3" t="n">
-        <v>7788</v>
+        <v>5800</v>
       </c>
       <c r="D3" t="n">
-        <v>16249</v>
+        <v>15811</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3302</v>
+        <v>2612</v>
       </c>
       <c r="C4" t="n">
-        <v>5083</v>
+        <v>4410</v>
       </c>
       <c r="D4" t="n">
-        <v>10141</v>
+        <v>8095</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2400</v>
+        <v>2009</v>
       </c>
       <c r="C5" t="n">
-        <v>3946</v>
+        <v>3643</v>
       </c>
       <c r="D5" t="n">
-        <v>4186</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1484</v>
+        <v>1345</v>
       </c>
       <c r="C6" t="n">
-        <v>2913</v>
+        <v>2728</v>
       </c>
       <c r="D6" t="n">
-        <v>1598</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>755</v>
+        <v>722</v>
       </c>
       <c r="C7" t="n">
-        <v>1810</v>
+        <v>1668</v>
       </c>
       <c r="D7" t="n">
-        <v>748</v>
+        <v>716</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="C8" t="n">
-        <v>1031</v>
+        <v>838</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>499</v>
+        <v>383</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>262</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1231,10 +1231,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
         <v>165</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11002</v>
+        <v>9176</v>
       </c>
       <c r="C2" t="n">
-        <v>10284</v>
+        <v>13149</v>
       </c>
       <c r="D2" t="n">
-        <v>32691</v>
+        <v>28097</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4955</v>
+        <v>4478</v>
       </c>
       <c r="C3" t="n">
-        <v>8133</v>
+        <v>7903</v>
       </c>
       <c r="D3" t="n">
-        <v>16875</v>
+        <v>15720</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3189</v>
+        <v>2745</v>
       </c>
       <c r="C4" t="n">
-        <v>6097</v>
+        <v>4916</v>
       </c>
       <c r="D4" t="n">
-        <v>10614</v>
+        <v>8956</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2482</v>
+        <v>2018</v>
       </c>
       <c r="C5" t="n">
-        <v>4306</v>
+        <v>3913</v>
       </c>
       <c r="D5" t="n">
-        <v>4876</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1681</v>
+        <v>1500</v>
       </c>
       <c r="C6" t="n">
-        <v>3313</v>
+        <v>3070</v>
       </c>
       <c r="D6" t="n">
-        <v>1949</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>933</v>
+        <v>881</v>
       </c>
       <c r="C7" t="n">
-        <v>2234</v>
+        <v>2124</v>
       </c>
       <c r="D7" t="n">
-        <v>849</v>
+        <v>804</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C8" t="n">
-        <v>1325</v>
+        <v>1171</v>
       </c>
       <c r="D8" t="n">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C9" t="n">
-        <v>702</v>
+        <v>561</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>345</v>
+        <v>288</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9911</v>
+        <v>8229</v>
       </c>
       <c r="C2" t="n">
-        <v>6993</v>
+        <v>8625</v>
       </c>
       <c r="D2" t="n">
-        <v>26962</v>
+        <v>22856</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5841</v>
+        <v>5276</v>
       </c>
       <c r="C3" t="n">
-        <v>11558</v>
+        <v>11368</v>
       </c>
       <c r="D3" t="n">
-        <v>18650</v>
+        <v>17377</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2293</v>
+        <v>1864</v>
       </c>
       <c r="C4" t="n">
-        <v>7470</v>
+        <v>6588</v>
       </c>
       <c r="D4" t="n">
-        <v>10299</v>
+        <v>8586</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1553</v>
+        <v>1386</v>
       </c>
       <c r="C5" t="n">
-        <v>3246</v>
+        <v>3008</v>
       </c>
       <c r="D5" t="n">
-        <v>3220</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>862</v>
+        <v>814</v>
       </c>
       <c r="C6" t="n">
-        <v>2189</v>
+        <v>2081</v>
       </c>
       <c r="D6" t="n">
-        <v>832</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C7" t="n">
-        <v>1298</v>
+        <v>1147</v>
       </c>
       <c r="D7" t="n">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C8" t="n">
-        <v>687</v>
+        <v>549</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>338</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6112</v>
+        <v>5137</v>
       </c>
       <c r="C2" t="n">
-        <v>3742</v>
+        <v>3819</v>
       </c>
       <c r="D2" t="n">
-        <v>18598</v>
+        <v>16270</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6456</v>
+        <v>5641</v>
       </c>
       <c r="C3" t="n">
-        <v>8622</v>
+        <v>9113</v>
       </c>
       <c r="D3" t="n">
-        <v>18706</v>
+        <v>17304</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3157</v>
+        <v>2777</v>
       </c>
       <c r="C4" t="n">
-        <v>9413</v>
+        <v>8935</v>
       </c>
       <c r="D4" t="n">
-        <v>11466</v>
+        <v>9757</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1736</v>
+        <v>1517</v>
       </c>
       <c r="C5" t="n">
-        <v>5077</v>
+        <v>4636</v>
       </c>
       <c r="D5" t="n">
-        <v>4067</v>
+        <v>3452</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1022</v>
+        <v>979</v>
       </c>
       <c r="C6" t="n">
-        <v>2687</v>
+        <v>2545</v>
       </c>
       <c r="D6" t="n">
-        <v>1075</v>
+        <v>980</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C7" t="n">
-        <v>1635</v>
+        <v>1501</v>
       </c>
       <c r="D7" t="n">
-        <v>530</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>895</v>
+        <v>741</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6115</v>
+        <v>6534</v>
       </c>
       <c r="C2" t="n">
-        <v>4368</v>
+        <v>5646</v>
       </c>
       <c r="D2" t="n">
-        <v>28791</v>
+        <v>16042</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5347</v>
+        <v>4547</v>
       </c>
       <c r="C3" t="n">
-        <v>5612</v>
+        <v>5761</v>
       </c>
       <c r="D3" t="n">
-        <v>17434</v>
+        <v>15964</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3895</v>
+        <v>3486</v>
       </c>
       <c r="C4" t="n">
-        <v>8829</v>
+        <v>8839</v>
       </c>
       <c r="D4" t="n">
-        <v>12299</v>
+        <v>10764</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2075</v>
+        <v>1829</v>
       </c>
       <c r="C5" t="n">
-        <v>7059</v>
+        <v>6688</v>
       </c>
       <c r="D5" t="n">
-        <v>5079</v>
+        <v>4376</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1219</v>
+        <v>1115</v>
       </c>
       <c r="C6" t="n">
-        <v>3716</v>
+        <v>3483</v>
       </c>
       <c r="D6" t="n">
-        <v>1491</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C7" t="n">
-        <v>2103</v>
+        <v>1985</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -2422,10 +2422,10 @@
         <v>186</v>
       </c>
       <c r="C8" t="n">
-        <v>1200</v>
+        <v>1068</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>575</v>
+        <v>502</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3648</v>
+        <v>3811</v>
       </c>
       <c r="C2" t="n">
-        <v>2097</v>
+        <v>2581</v>
       </c>
       <c r="D2" t="n">
-        <v>20060</v>
+        <v>11103</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5382</v>
+        <v>4861</v>
       </c>
       <c r="C3" t="n">
-        <v>5023</v>
+        <v>5526</v>
       </c>
       <c r="D3" t="n">
-        <v>18224</v>
+        <v>15589</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4313</v>
+        <v>3872</v>
       </c>
       <c r="C4" t="n">
-        <v>8442</v>
+        <v>8439</v>
       </c>
       <c r="D4" t="n">
-        <v>13007</v>
+        <v>11452</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2145</v>
+        <v>1935</v>
       </c>
       <c r="C5" t="n">
-        <v>8520</v>
+        <v>8144</v>
       </c>
       <c r="D5" t="n">
-        <v>5342</v>
+        <v>4746</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>998</v>
+        <v>964</v>
       </c>
       <c r="C6" t="n">
-        <v>4442</v>
+        <v>4329</v>
       </c>
       <c r="D6" t="n">
-        <v>1447</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="7">
@@ -2719,10 +2719,10 @@
         <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>2192</v>
+        <v>2043</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>928</v>
+        <v>837</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4092</v>
+        <v>5279</v>
       </c>
       <c r="C2" t="n">
-        <v>6931</v>
+        <v>6970</v>
       </c>
       <c r="D2" t="n">
-        <v>18504</v>
+        <v>14698</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3993</v>
+        <v>3765</v>
       </c>
       <c r="C3" t="n">
-        <v>3298</v>
+        <v>3652</v>
       </c>
       <c r="D3" t="n">
-        <v>17423</v>
+        <v>13931</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4176</v>
+        <v>3734</v>
       </c>
       <c r="C4" t="n">
-        <v>6739</v>
+        <v>6918</v>
       </c>
       <c r="D4" t="n">
-        <v>13412</v>
+        <v>11779</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2653</v>
+        <v>2418</v>
       </c>
       <c r="C5" t="n">
-        <v>8390</v>
+        <v>8188</v>
       </c>
       <c r="D5" t="n">
-        <v>6283</v>
+        <v>5631</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1287</v>
+        <v>1231</v>
       </c>
       <c r="C6" t="n">
-        <v>6128</v>
+        <v>5978</v>
       </c>
       <c r="D6" t="n">
-        <v>1951</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C7" t="n">
-        <v>3116</v>
+        <v>3023</v>
       </c>
       <c r="D7" t="n">
-        <v>702</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1391</v>
+        <v>1302</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>487</v>
+        <v>457</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2934</v>
+        <v>3558</v>
       </c>
       <c r="C2" t="n">
-        <v>3693</v>
+        <v>4569</v>
       </c>
       <c r="D2" t="n">
-        <v>13270</v>
+        <v>10622</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3527</v>
+        <v>3733</v>
       </c>
       <c r="C3" t="n">
-        <v>4276</v>
+        <v>4563</v>
       </c>
       <c r="D3" t="n">
-        <v>16772</v>
+        <v>13265</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3795</v>
+        <v>3444</v>
       </c>
       <c r="C4" t="n">
-        <v>5405</v>
+        <v>5625</v>
       </c>
       <c r="D4" t="n">
-        <v>13633</v>
+        <v>11823</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2939</v>
+        <v>2653</v>
       </c>
       <c r="C5" t="n">
-        <v>7951</v>
+        <v>7790</v>
       </c>
       <c r="D5" t="n">
-        <v>6905</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1510</v>
+        <v>1462</v>
       </c>
       <c r="C6" t="n">
-        <v>7060</v>
+        <v>6929</v>
       </c>
       <c r="D6" t="n">
-        <v>2359</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="C7" t="n">
-        <v>4036</v>
+        <v>3982</v>
       </c>
       <c r="D7" t="n">
-        <v>788</v>
+        <v>763</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1790</v>
+        <v>1720</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4921</v>
+        <v>4367</v>
       </c>
       <c r="C2" t="n">
-        <v>8757</v>
+        <v>11412</v>
       </c>
       <c r="D2" t="n">
-        <v>18299</v>
+        <v>18421</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2798</v>
+        <v>3088</v>
       </c>
       <c r="C3" t="n">
-        <v>3598</v>
+        <v>4054</v>
       </c>
       <c r="D3" t="n">
-        <v>15278</v>
+        <v>12098</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3218</v>
+        <v>3081</v>
       </c>
       <c r="C4" t="n">
-        <v>4815</v>
+        <v>5049</v>
       </c>
       <c r="D4" t="n">
-        <v>13670</v>
+        <v>11671</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2940</v>
+        <v>2664</v>
       </c>
       <c r="C5" t="n">
-        <v>6759</v>
+        <v>6734</v>
       </c>
       <c r="D5" t="n">
-        <v>7599</v>
+        <v>6770</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1846</v>
+        <v>1743</v>
       </c>
       <c r="C6" t="n">
-        <v>7342</v>
+        <v>7208</v>
       </c>
       <c r="D6" t="n">
-        <v>2896</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="C7" t="n">
-        <v>5200</v>
+        <v>5145</v>
       </c>
       <c r="D7" t="n">
-        <v>964</v>
+        <v>932</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>2559</v>
+        <v>2517</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6902</v>
+        <v>5328</v>
       </c>
       <c r="C2" t="n">
-        <v>5668</v>
+        <v>2573</v>
       </c>
       <c r="D2" t="n">
-        <v>9116</v>
+        <v>6798</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3561</v>
+        <v>3127</v>
       </c>
       <c r="C2" t="n">
-        <v>5044</v>
+        <v>6482</v>
       </c>
       <c r="D2" t="n">
-        <v>13615</v>
+        <v>13557</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3819</v>
+        <v>3986</v>
       </c>
       <c r="C3" t="n">
-        <v>5070</v>
+        <v>6111</v>
       </c>
       <c r="D3" t="n">
-        <v>16610</v>
+        <v>13577</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4362</v>
+        <v>4041</v>
       </c>
       <c r="C4" t="n">
-        <v>7109</v>
+        <v>7343</v>
       </c>
       <c r="D4" t="n">
-        <v>14028</v>
+        <v>11979</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1760</v>
+        <v>1684</v>
       </c>
       <c r="C5" t="n">
-        <v>10175</v>
+        <v>10047</v>
       </c>
       <c r="D5" t="n">
-        <v>6890</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="C6" t="n">
-        <v>6463</v>
+        <v>6454</v>
       </c>
       <c r="D6" t="n">
-        <v>2240</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>2507</v>
+        <v>2466</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>938</v>
+        <v>926</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7997</v>
+        <v>7326</v>
       </c>
       <c r="C2" t="n">
-        <v>6069</v>
+        <v>3055</v>
       </c>
       <c r="D2" t="n">
-        <v>24857</v>
+        <v>12354</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2932</v>
+        <v>2264</v>
       </c>
       <c r="C3" t="n">
-        <v>2856</v>
+        <v>1317</v>
       </c>
       <c r="D3" t="n">
-        <v>2170</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4979</v>
+        <v>4838</v>
       </c>
       <c r="C2" t="n">
-        <v>3490</v>
+        <v>7214</v>
       </c>
       <c r="D2" t="n">
-        <v>29176</v>
+        <v>27572</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4486</v>
+        <v>3992</v>
       </c>
       <c r="C3" t="n">
-        <v>4030</v>
+        <v>1995</v>
       </c>
       <c r="D3" t="n">
-        <v>5821</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1308</v>
+        <v>1017</v>
       </c>
       <c r="C4" t="n">
-        <v>1717</v>
+        <v>827</v>
       </c>
       <c r="D4" t="n">
-        <v>1618</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
         <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4910,7 +4910,7 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
         <v>441</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6931</v>
+        <v>5961</v>
       </c>
       <c r="C2" t="n">
-        <v>4178</v>
+        <v>4152</v>
       </c>
       <c r="D2" t="n">
-        <v>33818</v>
+        <v>21884</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3901</v>
+        <v>3669</v>
       </c>
       <c r="C3" t="n">
-        <v>3233</v>
+        <v>4190</v>
       </c>
       <c r="D3" t="n">
-        <v>9138</v>
+        <v>7074</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2463</v>
+        <v>2117</v>
       </c>
       <c r="C4" t="n">
-        <v>2991</v>
+        <v>1463</v>
       </c>
       <c r="D4" t="n">
-        <v>2375</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>585</v>
+        <v>478</v>
       </c>
       <c r="C5" t="n">
-        <v>1034</v>
+        <v>553</v>
       </c>
       <c r="D5" t="n">
-        <v>1226</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6518</v>
+        <v>5632</v>
       </c>
       <c r="C2" t="n">
-        <v>6972</v>
+        <v>5219</v>
       </c>
       <c r="D2" t="n">
-        <v>31242</v>
+        <v>19260</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4400</v>
+        <v>3945</v>
       </c>
       <c r="C3" t="n">
-        <v>3237</v>
+        <v>3622</v>
       </c>
       <c r="D3" t="n">
-        <v>12246</v>
+        <v>8827</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2683</v>
+        <v>2443</v>
       </c>
       <c r="C4" t="n">
-        <v>3058</v>
+        <v>2924</v>
       </c>
       <c r="D4" t="n">
-        <v>3536</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1247</v>
+        <v>1072</v>
       </c>
       <c r="C5" t="n">
-        <v>2027</v>
+        <v>1016</v>
       </c>
       <c r="D5" t="n">
-        <v>1375</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="C6" t="n">
-        <v>662</v>
+        <v>429</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>942</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5599,7 +5599,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>128</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8280</v>
+        <v>5730</v>
       </c>
       <c r="C2" t="n">
-        <v>7807</v>
+        <v>7234</v>
       </c>
       <c r="D2" t="n">
-        <v>38888</v>
+        <v>23522</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3948</v>
+        <v>3484</v>
       </c>
       <c r="C3" t="n">
-        <v>4215</v>
+        <v>3646</v>
       </c>
       <c r="D3" t="n">
-        <v>13426</v>
+        <v>9212</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2182</v>
+        <v>1982</v>
       </c>
       <c r="C4" t="n">
-        <v>2585</v>
+        <v>2697</v>
       </c>
       <c r="D4" t="n">
-        <v>4380</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1033</v>
+        <v>928</v>
       </c>
       <c r="C5" t="n">
-        <v>1855</v>
+        <v>1498</v>
       </c>
       <c r="D5" t="n">
-        <v>1371</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>366</v>
+        <v>319</v>
       </c>
       <c r="C6" t="n">
-        <v>909</v>
+        <v>492</v>
       </c>
       <c r="D6" t="n">
-        <v>775</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>322</v>
+        <v>248</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
         <v>361</v>
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
         <v>235</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5986,7 +5986,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6309</v>
+        <v>5037</v>
       </c>
       <c r="C2" t="n">
-        <v>5595</v>
+        <v>4357</v>
       </c>
       <c r="D2" t="n">
-        <v>27773</v>
+        <v>32867</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5125</v>
+        <v>3840</v>
       </c>
       <c r="C3" t="n">
-        <v>5431</v>
+        <v>4986</v>
       </c>
       <c r="D3" t="n">
-        <v>16715</v>
+        <v>11037</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2660</v>
+        <v>2396</v>
       </c>
       <c r="C4" t="n">
-        <v>3517</v>
+        <v>3233</v>
       </c>
       <c r="D4" t="n">
-        <v>6028</v>
+        <v>4417</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1434</v>
+        <v>1315</v>
       </c>
       <c r="C5" t="n">
-        <v>2243</v>
+        <v>2191</v>
       </c>
       <c r="D5" t="n">
-        <v>1935</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>643</v>
+        <v>587</v>
       </c>
       <c r="C6" t="n">
-        <v>1433</v>
+        <v>1074</v>
       </c>
       <c r="D6" t="n">
-        <v>878</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="C7" t="n">
-        <v>649</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6185,7 +6185,7 @@
         <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6049</v>
+        <v>4636</v>
       </c>
       <c r="C2" t="n">
-        <v>8754</v>
+        <v>7506</v>
       </c>
       <c r="D2" t="n">
-        <v>21347</v>
+        <v>27798</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4700</v>
+        <v>3658</v>
       </c>
       <c r="C3" t="n">
-        <v>4778</v>
+        <v>3992</v>
       </c>
       <c r="D3" t="n">
-        <v>17280</v>
+        <v>13892</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3340</v>
+        <v>2709</v>
       </c>
       <c r="C4" t="n">
-        <v>4527</v>
+        <v>4192</v>
       </c>
       <c r="D4" t="n">
-        <v>7896</v>
+        <v>5617</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1780</v>
+        <v>1632</v>
       </c>
       <c r="C5" t="n">
-        <v>2893</v>
+        <v>2735</v>
       </c>
       <c r="D5" t="n">
-        <v>2604</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>942</v>
+        <v>876</v>
       </c>
       <c r="C6" t="n">
-        <v>1844</v>
+        <v>1662</v>
       </c>
       <c r="D6" t="n">
-        <v>1058</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="C7" t="n">
-        <v>1049</v>
+        <v>764</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>464</v>
+        <v>316</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_12_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_12_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6972</v>
+        <v>4443</v>
       </c>
       <c r="C2" t="n">
-        <v>8171</v>
+        <v>5927</v>
       </c>
       <c r="D2" t="n">
-        <v>27652</v>
+        <v>26376</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3394</v>
+        <v>2886</v>
       </c>
       <c r="C3" t="n">
-        <v>5070</v>
+        <v>5822</v>
       </c>
       <c r="D3" t="n">
-        <v>15027</v>
+        <v>14516</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2711</v>
+        <v>2396</v>
       </c>
       <c r="C4" t="n">
-        <v>3995</v>
+        <v>5971</v>
       </c>
       <c r="D4" t="n">
-        <v>6901</v>
+        <v>9111</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1906</v>
+        <v>1579</v>
       </c>
       <c r="C5" t="n">
-        <v>3447</v>
+        <v>6036</v>
       </c>
       <c r="D5" t="n">
-        <v>2665</v>
+        <v>3829</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1124</v>
+        <v>875</v>
       </c>
       <c r="C6" t="n">
-        <v>2173</v>
+        <v>4246</v>
       </c>
       <c r="D6" t="n">
-        <v>1138</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>536</v>
+        <v>384</v>
       </c>
       <c r="C7" t="n">
-        <v>1221</v>
+        <v>2164</v>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
+        <v>142</v>
       </c>
       <c r="C8" t="n">
-        <v>535</v>
+        <v>868</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7490</v>
+        <v>5108</v>
       </c>
       <c r="C2" t="n">
-        <v>13041</v>
+        <v>5609</v>
       </c>
       <c r="D2" t="n">
-        <v>23207</v>
+        <v>32022</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4073</v>
+        <v>2921</v>
       </c>
       <c r="C3" t="n">
-        <v>5800</v>
+        <v>5190</v>
       </c>
       <c r="D3" t="n">
-        <v>15811</v>
+        <v>15081</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2612</v>
+        <v>2224</v>
       </c>
       <c r="C4" t="n">
-        <v>4410</v>
+        <v>5722</v>
       </c>
       <c r="D4" t="n">
-        <v>8095</v>
+        <v>9576</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2009</v>
+        <v>1694</v>
       </c>
       <c r="C5" t="n">
-        <v>3643</v>
+        <v>5823</v>
       </c>
       <c r="D5" t="n">
-        <v>3249</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1345</v>
+        <v>1057</v>
       </c>
       <c r="C6" t="n">
-        <v>2728</v>
+        <v>4979</v>
       </c>
       <c r="D6" t="n">
-        <v>1371</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>722</v>
+        <v>525</v>
       </c>
       <c r="C7" t="n">
-        <v>1668</v>
+        <v>3019</v>
       </c>
       <c r="D7" t="n">
-        <v>716</v>
+        <v>811</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>300</v>
+        <v>208</v>
       </c>
       <c r="C8" t="n">
-        <v>838</v>
+        <v>1401</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>383</v>
+        <v>538</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9176</v>
+        <v>5507</v>
       </c>
       <c r="C2" t="n">
-        <v>13149</v>
+        <v>7155</v>
       </c>
       <c r="D2" t="n">
-        <v>28097</v>
+        <v>39396</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4478</v>
+        <v>3063</v>
       </c>
       <c r="C3" t="n">
-        <v>7903</v>
+        <v>4769</v>
       </c>
       <c r="D3" t="n">
-        <v>15720</v>
+        <v>16148</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2745</v>
+        <v>2127</v>
       </c>
       <c r="C4" t="n">
-        <v>4916</v>
+        <v>5328</v>
       </c>
       <c r="D4" t="n">
-        <v>8956</v>
+        <v>10077</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2018</v>
+        <v>1696</v>
       </c>
       <c r="C5" t="n">
-        <v>3913</v>
+        <v>5661</v>
       </c>
       <c r="D5" t="n">
-        <v>3894</v>
+        <v>5021</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1500</v>
+        <v>1196</v>
       </c>
       <c r="C6" t="n">
-        <v>3070</v>
+        <v>5212</v>
       </c>
       <c r="D6" t="n">
-        <v>1609</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>881</v>
+        <v>647</v>
       </c>
       <c r="C7" t="n">
-        <v>2124</v>
+        <v>3737</v>
       </c>
       <c r="D7" t="n">
-        <v>804</v>
+        <v>920</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>416</v>
+        <v>284</v>
       </c>
       <c r="C8" t="n">
-        <v>1171</v>
+        <v>1989</v>
       </c>
       <c r="D8" t="n">
-        <v>490</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="C9" t="n">
-        <v>561</v>
+        <v>850</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>288</v>
+        <v>348</v>
       </c>
       <c r="D10" t="n">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8229</v>
+        <v>5116</v>
       </c>
       <c r="C2" t="n">
-        <v>8625</v>
+        <v>4979</v>
       </c>
       <c r="D2" t="n">
-        <v>22856</v>
+        <v>32291</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5276</v>
+        <v>3717</v>
       </c>
       <c r="C3" t="n">
-        <v>11368</v>
+        <v>7624</v>
       </c>
       <c r="D3" t="n">
-        <v>17377</v>
+        <v>17822</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1864</v>
+        <v>1567</v>
       </c>
       <c r="C4" t="n">
-        <v>6588</v>
+        <v>8247</v>
       </c>
       <c r="D4" t="n">
-        <v>8586</v>
+        <v>10048</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1386</v>
+        <v>1105</v>
       </c>
       <c r="C5" t="n">
-        <v>3008</v>
+        <v>5107</v>
       </c>
       <c r="D5" t="n">
-        <v>2660</v>
+        <v>3444</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>814</v>
+        <v>597</v>
       </c>
       <c r="C6" t="n">
-        <v>2081</v>
+        <v>3662</v>
       </c>
       <c r="D6" t="n">
-        <v>787</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>384</v>
+        <v>262</v>
       </c>
       <c r="C7" t="n">
-        <v>1147</v>
+        <v>1949</v>
       </c>
       <c r="D7" t="n">
-        <v>480</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>549</v>
+        <v>833</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>282</v>
+        <v>341</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5137</v>
+        <v>3123</v>
       </c>
       <c r="C2" t="n">
-        <v>3819</v>
+        <v>2407</v>
       </c>
       <c r="D2" t="n">
-        <v>16270</v>
+        <v>22166</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5641</v>
+        <v>3718</v>
       </c>
       <c r="C3" t="n">
-        <v>9113</v>
+        <v>5870</v>
       </c>
       <c r="D3" t="n">
-        <v>17304</v>
+        <v>18934</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2777</v>
+        <v>2059</v>
       </c>
       <c r="C4" t="n">
-        <v>8935</v>
+        <v>8111</v>
       </c>
       <c r="D4" t="n">
-        <v>9757</v>
+        <v>11054</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1517</v>
+        <v>1218</v>
       </c>
       <c r="C5" t="n">
-        <v>4636</v>
+        <v>6481</v>
       </c>
       <c r="D5" t="n">
-        <v>3452</v>
+        <v>4166</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>979</v>
+        <v>703</v>
       </c>
       <c r="C6" t="n">
-        <v>2545</v>
+        <v>4322</v>
       </c>
       <c r="D6" t="n">
-        <v>980</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>363</v>
+        <v>245</v>
       </c>
       <c r="C7" t="n">
-        <v>1501</v>
+        <v>2556</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="C8" t="n">
-        <v>741</v>
+        <v>1116</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C9" t="n">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6534</v>
+        <v>3628</v>
       </c>
       <c r="C2" t="n">
-        <v>5646</v>
+        <v>11657</v>
       </c>
       <c r="D2" t="n">
-        <v>16042</v>
+        <v>21948</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4547</v>
+        <v>2924</v>
       </c>
       <c r="C3" t="n">
-        <v>5761</v>
+        <v>3780</v>
       </c>
       <c r="D3" t="n">
-        <v>15964</v>
+        <v>18101</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3486</v>
+        <v>2354</v>
       </c>
       <c r="C4" t="n">
-        <v>8839</v>
+        <v>6866</v>
       </c>
       <c r="D4" t="n">
-        <v>10764</v>
+        <v>12003</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1829</v>
+        <v>1398</v>
       </c>
       <c r="C5" t="n">
-        <v>6688</v>
+        <v>7159</v>
       </c>
       <c r="D5" t="n">
-        <v>4376</v>
+        <v>5097</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1115</v>
+        <v>842</v>
       </c>
       <c r="C6" t="n">
-        <v>3483</v>
+        <v>5214</v>
       </c>
       <c r="D6" t="n">
-        <v>1346</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>542</v>
+        <v>364</v>
       </c>
       <c r="C7" t="n">
-        <v>1985</v>
+        <v>3324</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>186</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>1068</v>
+        <v>1690</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>502</v>
+        <v>647</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3811</v>
+        <v>2150</v>
       </c>
       <c r="C2" t="n">
-        <v>2581</v>
+        <v>5536</v>
       </c>
       <c r="D2" t="n">
-        <v>11103</v>
+        <v>15307</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4861</v>
+        <v>3004</v>
       </c>
       <c r="C3" t="n">
-        <v>5526</v>
+        <v>6254</v>
       </c>
       <c r="D3" t="n">
-        <v>15589</v>
+        <v>18095</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3872</v>
+        <v>2575</v>
       </c>
       <c r="C4" t="n">
-        <v>8439</v>
+        <v>6470</v>
       </c>
       <c r="D4" t="n">
-        <v>11452</v>
+        <v>12790</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1935</v>
+        <v>1463</v>
       </c>
       <c r="C5" t="n">
-        <v>8144</v>
+        <v>8273</v>
       </c>
       <c r="D5" t="n">
-        <v>4746</v>
+        <v>5357</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>964</v>
+        <v>670</v>
       </c>
       <c r="C6" t="n">
-        <v>4329</v>
+        <v>6134</v>
       </c>
       <c r="D6" t="n">
-        <v>1324</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>2043</v>
+        <v>3309</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="C8" t="n">
-        <v>837</v>
+        <v>1130</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5279</v>
+        <v>2730</v>
       </c>
       <c r="C2" t="n">
-        <v>6970</v>
+        <v>7308</v>
       </c>
       <c r="D2" t="n">
-        <v>14698</v>
+        <v>14806</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3765</v>
+        <v>2274</v>
       </c>
       <c r="C3" t="n">
-        <v>3652</v>
+        <v>5292</v>
       </c>
       <c r="D3" t="n">
-        <v>13931</v>
+        <v>16551</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3734</v>
+        <v>2398</v>
       </c>
       <c r="C4" t="n">
-        <v>6918</v>
+        <v>6298</v>
       </c>
       <c r="D4" t="n">
-        <v>11779</v>
+        <v>13216</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2418</v>
+        <v>1700</v>
       </c>
       <c r="C5" t="n">
-        <v>8188</v>
+        <v>7401</v>
       </c>
       <c r="D5" t="n">
-        <v>5631</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1231</v>
+        <v>877</v>
       </c>
       <c r="C6" t="n">
-        <v>5978</v>
+        <v>7002</v>
       </c>
       <c r="D6" t="n">
-        <v>1812</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>372</v>
+        <v>245</v>
       </c>
       <c r="C7" t="n">
-        <v>3023</v>
+        <v>4419</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1302</v>
+        <v>1920</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>457</v>
+        <v>545</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3558</v>
+        <v>1725</v>
       </c>
       <c r="C2" t="n">
-        <v>4569</v>
+        <v>4777</v>
       </c>
       <c r="D2" t="n">
-        <v>10622</v>
+        <v>10645</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3733</v>
+        <v>2118</v>
       </c>
       <c r="C3" t="n">
-        <v>4563</v>
+        <v>5511</v>
       </c>
       <c r="D3" t="n">
-        <v>13265</v>
+        <v>15481</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3444</v>
+        <v>2175</v>
       </c>
       <c r="C4" t="n">
-        <v>5625</v>
+        <v>5952</v>
       </c>
       <c r="D4" t="n">
-        <v>11823</v>
+        <v>13357</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2653</v>
+        <v>1811</v>
       </c>
       <c r="C5" t="n">
-        <v>7790</v>
+        <v>7079</v>
       </c>
       <c r="D5" t="n">
-        <v>6276</v>
+        <v>6927</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1462</v>
+        <v>1019</v>
       </c>
       <c r="C6" t="n">
-        <v>6929</v>
+        <v>7486</v>
       </c>
       <c r="D6" t="n">
-        <v>2155</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>350</v>
+        <v>219</v>
       </c>
       <c r="C7" t="n">
-        <v>3982</v>
+        <v>5259</v>
       </c>
       <c r="D7" t="n">
-        <v>763</v>
+        <v>790</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n">
-        <v>1720</v>
+        <v>2506</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>550</v>
+        <v>604</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4367</v>
+        <v>2431</v>
       </c>
       <c r="C2" t="n">
-        <v>11412</v>
+        <v>19364</v>
       </c>
       <c r="D2" t="n">
-        <v>18421</v>
+        <v>11509</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3088</v>
+        <v>1669</v>
       </c>
       <c r="C3" t="n">
-        <v>4054</v>
+        <v>4658</v>
       </c>
       <c r="D3" t="n">
-        <v>12098</v>
+        <v>14058</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3081</v>
+        <v>1891</v>
       </c>
       <c r="C4" t="n">
-        <v>5049</v>
+        <v>5646</v>
       </c>
       <c r="D4" t="n">
-        <v>11671</v>
+        <v>13108</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2664</v>
+        <v>1764</v>
       </c>
       <c r="C5" t="n">
-        <v>6734</v>
+        <v>6488</v>
       </c>
       <c r="D5" t="n">
-        <v>6770</v>
+        <v>7580</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1743</v>
+        <v>1189</v>
       </c>
       <c r="C6" t="n">
-        <v>7208</v>
+        <v>7272</v>
       </c>
       <c r="D6" t="n">
-        <v>2680</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>631</v>
+        <v>408</v>
       </c>
       <c r="C7" t="n">
-        <v>5145</v>
+        <v>6064</v>
       </c>
       <c r="D7" t="n">
-        <v>932</v>
+        <v>966</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>2517</v>
+        <v>3473</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>945</v>
+        <v>1206</v>
       </c>
       <c r="D9" t="n">
-        <v>314</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>324</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5328</v>
+        <v>4171</v>
       </c>
       <c r="C2" t="n">
-        <v>2573</v>
+        <v>5479</v>
       </c>
       <c r="D2" t="n">
-        <v>6798</v>
+        <v>23136</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3127</v>
+        <v>1756</v>
       </c>
       <c r="C2" t="n">
-        <v>6482</v>
+        <v>11308</v>
       </c>
       <c r="D2" t="n">
-        <v>13557</v>
+        <v>8562</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3986</v>
+        <v>2244</v>
       </c>
       <c r="C3" t="n">
-        <v>6111</v>
+        <v>8251</v>
       </c>
       <c r="D3" t="n">
-        <v>13577</v>
+        <v>15021</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4041</v>
+        <v>2580</v>
       </c>
       <c r="C4" t="n">
-        <v>7343</v>
+        <v>7940</v>
       </c>
       <c r="D4" t="n">
-        <v>11979</v>
+        <v>13522</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1684</v>
+        <v>1131</v>
       </c>
       <c r="C5" t="n">
-        <v>10047</v>
+        <v>9883</v>
       </c>
       <c r="D5" t="n">
-        <v>6252</v>
+        <v>6906</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>583</v>
+        <v>376</v>
       </c>
       <c r="C6" t="n">
-        <v>6454</v>
+        <v>7296</v>
       </c>
       <c r="D6" t="n">
-        <v>2107</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2466</v>
+        <v>3403</v>
       </c>
       <c r="D7" t="n">
-        <v>577</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>926</v>
+        <v>1181</v>
       </c>
       <c r="D8" t="n">
-        <v>307</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7326</v>
+        <v>5803</v>
       </c>
       <c r="C2" t="n">
-        <v>3055</v>
+        <v>8664</v>
       </c>
       <c r="D2" t="n">
-        <v>12354</v>
+        <v>34543</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2264</v>
+        <v>1774</v>
       </c>
       <c r="C3" t="n">
-        <v>1317</v>
+        <v>2761</v>
       </c>
       <c r="D3" t="n">
-        <v>1835</v>
+        <v>4526</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4838</v>
+        <v>4618</v>
       </c>
       <c r="C2" t="n">
-        <v>7214</v>
+        <v>11249</v>
       </c>
       <c r="D2" t="n">
-        <v>27572</v>
+        <v>28087</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3992</v>
+        <v>3108</v>
       </c>
       <c r="C3" t="n">
-        <v>1995</v>
+        <v>5261</v>
       </c>
       <c r="D3" t="n">
-        <v>3467</v>
+        <v>9235</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1017</v>
+        <v>805</v>
       </c>
       <c r="C4" t="n">
-        <v>827</v>
+        <v>1662</v>
       </c>
       <c r="D4" t="n">
-        <v>1551</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5961</v>
+        <v>5130</v>
       </c>
       <c r="C2" t="n">
-        <v>4152</v>
+        <v>10153</v>
       </c>
       <c r="D2" t="n">
-        <v>21884</v>
+        <v>31680</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3669</v>
+        <v>3187</v>
       </c>
       <c r="C3" t="n">
-        <v>4190</v>
+        <v>7340</v>
       </c>
       <c r="D3" t="n">
-        <v>7074</v>
+        <v>11586</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2117</v>
+        <v>1634</v>
       </c>
       <c r="C4" t="n">
-        <v>1463</v>
+        <v>3631</v>
       </c>
       <c r="D4" t="n">
-        <v>1856</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>478</v>
+        <v>385</v>
       </c>
       <c r="C5" t="n">
-        <v>553</v>
+        <v>990</v>
       </c>
       <c r="D5" t="n">
-        <v>1220</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>115</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5632</v>
+        <v>4897</v>
       </c>
       <c r="C2" t="n">
-        <v>5219</v>
+        <v>12227</v>
       </c>
       <c r="D2" t="n">
-        <v>19260</v>
+        <v>28942</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3945</v>
+        <v>3354</v>
       </c>
       <c r="C3" t="n">
-        <v>3622</v>
+        <v>7638</v>
       </c>
       <c r="D3" t="n">
-        <v>8827</v>
+        <v>13824</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2443</v>
+        <v>2028</v>
       </c>
       <c r="C4" t="n">
-        <v>2924</v>
+        <v>5513</v>
       </c>
       <c r="D4" t="n">
-        <v>2733</v>
+        <v>4789</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1072</v>
+        <v>815</v>
       </c>
       <c r="C5" t="n">
-        <v>1016</v>
+        <v>2303</v>
       </c>
       <c r="D5" t="n">
-        <v>1298</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="C6" t="n">
-        <v>429</v>
+        <v>644</v>
       </c>
       <c r="D6" t="n">
-        <v>942</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5730</v>
+        <v>6024</v>
       </c>
       <c r="C2" t="n">
-        <v>7234</v>
+        <v>8494</v>
       </c>
       <c r="D2" t="n">
-        <v>23522</v>
+        <v>24528</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3484</v>
+        <v>2970</v>
       </c>
       <c r="C3" t="n">
-        <v>3646</v>
+        <v>8146</v>
       </c>
       <c r="D3" t="n">
-        <v>9212</v>
+        <v>14376</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1982</v>
+        <v>1646</v>
       </c>
       <c r="C4" t="n">
-        <v>2697</v>
+        <v>5451</v>
       </c>
       <c r="D4" t="n">
-        <v>3260</v>
+        <v>5365</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>928</v>
+        <v>733</v>
       </c>
       <c r="C5" t="n">
-        <v>1498</v>
+        <v>2877</v>
       </c>
       <c r="D5" t="n">
-        <v>1232</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="C6" t="n">
-        <v>492</v>
+        <v>969</v>
       </c>
       <c r="D6" t="n">
-        <v>756</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C7" t="n">
-        <v>248</v>
+        <v>316</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5986,7 +5986,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -5997,10 +5997,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5037</v>
+        <v>4364</v>
       </c>
       <c r="C2" t="n">
-        <v>4357</v>
+        <v>5171</v>
       </c>
       <c r="D2" t="n">
-        <v>32867</v>
+        <v>21401</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3840</v>
+        <v>3697</v>
       </c>
       <c r="C3" t="n">
-        <v>4986</v>
+        <v>7194</v>
       </c>
       <c r="D3" t="n">
-        <v>11037</v>
+        <v>15023</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2396</v>
+        <v>1991</v>
       </c>
       <c r="C4" t="n">
-        <v>3233</v>
+        <v>6863</v>
       </c>
       <c r="D4" t="n">
-        <v>4417</v>
+        <v>7018</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1315</v>
+        <v>1053</v>
       </c>
       <c r="C5" t="n">
-        <v>2191</v>
+        <v>4299</v>
       </c>
       <c r="D5" t="n">
-        <v>1591</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>587</v>
+        <v>445</v>
       </c>
       <c r="C6" t="n">
-        <v>1074</v>
+        <v>2019</v>
       </c>
       <c r="D6" t="n">
-        <v>841</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>388</v>
+        <v>674</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>236</v>
+        <v>270</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4636</v>
+        <v>3719</v>
       </c>
       <c r="C2" t="n">
-        <v>7506</v>
+        <v>8096</v>
       </c>
       <c r="D2" t="n">
-        <v>27798</v>
+        <v>19170</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3658</v>
+        <v>3310</v>
       </c>
       <c r="C3" t="n">
-        <v>3992</v>
+        <v>5327</v>
       </c>
       <c r="D3" t="n">
-        <v>13892</v>
+        <v>14934</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2709</v>
+        <v>2396</v>
       </c>
       <c r="C4" t="n">
-        <v>4192</v>
+        <v>6901</v>
       </c>
       <c r="D4" t="n">
-        <v>5617</v>
+        <v>8197</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1632</v>
+        <v>1325</v>
       </c>
       <c r="C5" t="n">
-        <v>2735</v>
+        <v>5563</v>
       </c>
       <c r="D5" t="n">
-        <v>2085</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>876</v>
+        <v>662</v>
       </c>
       <c r="C6" t="n">
-        <v>1662</v>
+        <v>3137</v>
       </c>
       <c r="D6" t="n">
-        <v>957</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>346</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>764</v>
+        <v>1359</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>316</v>
+        <v>467</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_12_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_12_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4443</v>
+        <v>1702</v>
       </c>
       <c r="C2" t="n">
-        <v>5927</v>
+        <v>3873</v>
       </c>
       <c r="D2" t="n">
-        <v>26376</v>
+        <v>22522</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2886</v>
+        <v>2544</v>
       </c>
       <c r="C3" t="n">
-        <v>5822</v>
+        <v>6895</v>
       </c>
       <c r="D3" t="n">
-        <v>14516</v>
+        <v>17977</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2396</v>
+        <v>1369</v>
       </c>
       <c r="C4" t="n">
-        <v>5971</v>
+        <v>8811</v>
       </c>
       <c r="D4" t="n">
-        <v>9111</v>
+        <v>7441</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1579</v>
+        <v>600</v>
       </c>
       <c r="C5" t="n">
-        <v>6036</v>
+        <v>6255</v>
       </c>
       <c r="D5" t="n">
-        <v>3829</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>875</v>
+        <v>258</v>
       </c>
       <c r="C6" t="n">
-        <v>4246</v>
+        <v>2410</v>
       </c>
       <c r="D6" t="n">
-        <v>1493</v>
+        <v>744</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>384</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>2164</v>
+        <v>770</v>
       </c>
       <c r="D7" t="n">
-        <v>702</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>868</v>
+        <v>349</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>332</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5108</v>
+        <v>1147</v>
       </c>
       <c r="C2" t="n">
-        <v>5609</v>
+        <v>4203</v>
       </c>
       <c r="D2" t="n">
-        <v>32022</v>
+        <v>23566</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2921</v>
+        <v>1840</v>
       </c>
       <c r="C3" t="n">
-        <v>5190</v>
+        <v>4682</v>
       </c>
       <c r="D3" t="n">
-        <v>15081</v>
+        <v>17574</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2224</v>
+        <v>1641</v>
       </c>
       <c r="C4" t="n">
-        <v>5722</v>
+        <v>7700</v>
       </c>
       <c r="D4" t="n">
-        <v>9576</v>
+        <v>9035</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1694</v>
+        <v>821</v>
       </c>
       <c r="C5" t="n">
-        <v>5823</v>
+        <v>7400</v>
       </c>
       <c r="D5" t="n">
-        <v>4523</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1057</v>
+        <v>365</v>
       </c>
       <c r="C6" t="n">
-        <v>4979</v>
+        <v>4254</v>
       </c>
       <c r="D6" t="n">
-        <v>1795</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>525</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>3019</v>
+        <v>1532</v>
       </c>
       <c r="D7" t="n">
-        <v>811</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1401</v>
+        <v>533</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>538</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5507</v>
+        <v>628</v>
       </c>
       <c r="C2" t="n">
-        <v>7155</v>
+        <v>1836</v>
       </c>
       <c r="D2" t="n">
-        <v>39396</v>
+        <v>16041</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3063</v>
+        <v>1594</v>
       </c>
       <c r="C3" t="n">
-        <v>4769</v>
+        <v>4333</v>
       </c>
       <c r="D3" t="n">
-        <v>16148</v>
+        <v>17843</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2127</v>
+        <v>1793</v>
       </c>
       <c r="C4" t="n">
-        <v>5328</v>
+        <v>7178</v>
       </c>
       <c r="D4" t="n">
-        <v>10077</v>
+        <v>10095</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1696</v>
+        <v>808</v>
       </c>
       <c r="C5" t="n">
-        <v>5661</v>
+        <v>8469</v>
       </c>
       <c r="D5" t="n">
-        <v>5021</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1196</v>
+        <v>292</v>
       </c>
       <c r="C6" t="n">
-        <v>5212</v>
+        <v>5160</v>
       </c>
       <c r="D6" t="n">
-        <v>2138</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>647</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>3737</v>
+        <v>1410</v>
       </c>
       <c r="D7" t="n">
-        <v>920</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>284</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1989</v>
+        <v>481</v>
       </c>
       <c r="D8" t="n">
-        <v>501</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>850</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>348</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>200</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>149</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5116</v>
+        <v>1140</v>
       </c>
       <c r="C2" t="n">
-        <v>4979</v>
+        <v>7673</v>
       </c>
       <c r="D2" t="n">
-        <v>32291</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3717</v>
+        <v>1008</v>
       </c>
       <c r="C3" t="n">
-        <v>7624</v>
+        <v>2775</v>
       </c>
       <c r="D3" t="n">
-        <v>17822</v>
+        <v>16527</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1567</v>
+        <v>1517</v>
       </c>
       <c r="C4" t="n">
-        <v>8247</v>
+        <v>5677</v>
       </c>
       <c r="D4" t="n">
-        <v>10048</v>
+        <v>11052</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1105</v>
+        <v>1073</v>
       </c>
       <c r="C5" t="n">
-        <v>5107</v>
+        <v>7766</v>
       </c>
       <c r="D5" t="n">
-        <v>3444</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>597</v>
+        <v>445</v>
       </c>
       <c r="C6" t="n">
-        <v>3662</v>
+        <v>6622</v>
       </c>
       <c r="D6" t="n">
-        <v>901</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>262</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>1949</v>
+        <v>3017</v>
       </c>
       <c r="D7" t="n">
-        <v>490</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>833</v>
+        <v>845</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="D9" t="n">
-        <v>243</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
         <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3123</v>
+        <v>590</v>
       </c>
       <c r="C2" t="n">
-        <v>2407</v>
+        <v>4633</v>
       </c>
       <c r="D2" t="n">
-        <v>22166</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3718</v>
+        <v>921</v>
       </c>
       <c r="C3" t="n">
-        <v>5870</v>
+        <v>4411</v>
       </c>
       <c r="D3" t="n">
-        <v>18934</v>
+        <v>16047</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2059</v>
+        <v>1252</v>
       </c>
       <c r="C4" t="n">
-        <v>8111</v>
+        <v>4414</v>
       </c>
       <c r="D4" t="n">
-        <v>11054</v>
+        <v>11610</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1218</v>
+        <v>1165</v>
       </c>
       <c r="C5" t="n">
-        <v>6481</v>
+        <v>7080</v>
       </c>
       <c r="D5" t="n">
-        <v>4166</v>
+        <v>5077</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>703</v>
+        <v>554</v>
       </c>
       <c r="C6" t="n">
-        <v>4322</v>
+        <v>7346</v>
       </c>
       <c r="D6" t="n">
-        <v>1136</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>2556</v>
+        <v>4176</v>
       </c>
       <c r="D7" t="n">
-        <v>536</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1116</v>
+        <v>1311</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3628</v>
+        <v>1129</v>
       </c>
       <c r="C2" t="n">
-        <v>11657</v>
+        <v>6930</v>
       </c>
       <c r="D2" t="n">
-        <v>21948</v>
+        <v>14469</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2924</v>
+        <v>670</v>
       </c>
       <c r="C3" t="n">
-        <v>3780</v>
+        <v>4023</v>
       </c>
       <c r="D3" t="n">
-        <v>18101</v>
+        <v>14814</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2354</v>
+        <v>980</v>
       </c>
       <c r="C4" t="n">
-        <v>6866</v>
+        <v>4320</v>
       </c>
       <c r="D4" t="n">
-        <v>12003</v>
+        <v>11938</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1398</v>
+        <v>1105</v>
       </c>
       <c r="C5" t="n">
-        <v>7159</v>
+        <v>5781</v>
       </c>
       <c r="D5" t="n">
-        <v>5097</v>
+        <v>5863</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>842</v>
+        <v>713</v>
       </c>
       <c r="C6" t="n">
-        <v>5214</v>
+        <v>7170</v>
       </c>
       <c r="D6" t="n">
-        <v>1557</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>364</v>
+        <v>244</v>
       </c>
       <c r="C7" t="n">
-        <v>3324</v>
+        <v>5488</v>
       </c>
       <c r="D7" t="n">
-        <v>612</v>
+        <v>777</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1690</v>
+        <v>2390</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>647</v>
+        <v>719</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2150</v>
+        <v>785</v>
       </c>
       <c r="C2" t="n">
-        <v>5536</v>
+        <v>3769</v>
       </c>
       <c r="D2" t="n">
-        <v>15307</v>
+        <v>10533</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3004</v>
+        <v>980</v>
       </c>
       <c r="C3" t="n">
-        <v>6254</v>
+        <v>5095</v>
       </c>
       <c r="D3" t="n">
-        <v>18095</v>
+        <v>15950</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2575</v>
+        <v>1512</v>
       </c>
       <c r="C4" t="n">
-        <v>6470</v>
+        <v>6352</v>
       </c>
       <c r="D4" t="n">
-        <v>12790</v>
+        <v>12123</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1463</v>
+        <v>709</v>
       </c>
       <c r="C5" t="n">
-        <v>8273</v>
+        <v>9295</v>
       </c>
       <c r="D5" t="n">
-        <v>5357</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>670</v>
+        <v>225</v>
       </c>
       <c r="C6" t="n">
-        <v>6134</v>
+        <v>6994</v>
       </c>
       <c r="D6" t="n">
-        <v>1507</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>3309</v>
+        <v>2342</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1130</v>
+        <v>704</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2730</v>
+        <v>419</v>
       </c>
       <c r="C2" t="n">
-        <v>7308</v>
+        <v>2892</v>
       </c>
       <c r="D2" t="n">
-        <v>14806</v>
+        <v>7931</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2274</v>
+        <v>759</v>
       </c>
       <c r="C3" t="n">
-        <v>5292</v>
+        <v>3997</v>
       </c>
       <c r="D3" t="n">
-        <v>16551</v>
+        <v>14093</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2398</v>
+        <v>1056</v>
       </c>
       <c r="C4" t="n">
-        <v>6298</v>
+        <v>5385</v>
       </c>
       <c r="D4" t="n">
-        <v>13216</v>
+        <v>11857</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1700</v>
+        <v>717</v>
       </c>
       <c r="C5" t="n">
-        <v>7401</v>
+        <v>7063</v>
       </c>
       <c r="D5" t="n">
-        <v>6264</v>
+        <v>5523</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>877</v>
+        <v>230</v>
       </c>
       <c r="C6" t="n">
-        <v>7002</v>
+        <v>6518</v>
       </c>
       <c r="D6" t="n">
-        <v>2019</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>245</v>
+        <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>4419</v>
+        <v>3039</v>
       </c>
       <c r="D7" t="n">
-        <v>701</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1920</v>
+        <v>837</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>545</v>
+        <v>255</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>118</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1725</v>
+        <v>392</v>
       </c>
       <c r="C2" t="n">
-        <v>4777</v>
+        <v>10970</v>
       </c>
       <c r="D2" t="n">
-        <v>10645</v>
+        <v>8437</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2118</v>
+        <v>506</v>
       </c>
       <c r="C3" t="n">
-        <v>5511</v>
+        <v>2983</v>
       </c>
       <c r="D3" t="n">
-        <v>15481</v>
+        <v>12164</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2175</v>
+        <v>810</v>
       </c>
       <c r="C4" t="n">
-        <v>5952</v>
+        <v>4526</v>
       </c>
       <c r="D4" t="n">
-        <v>13357</v>
+        <v>11904</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1811</v>
+        <v>777</v>
       </c>
       <c r="C5" t="n">
-        <v>7079</v>
+        <v>6114</v>
       </c>
       <c r="D5" t="n">
-        <v>6927</v>
+        <v>6449</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1019</v>
+        <v>403</v>
       </c>
       <c r="C6" t="n">
-        <v>7486</v>
+        <v>6715</v>
       </c>
       <c r="D6" t="n">
-        <v>2360</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>219</v>
+        <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>5259</v>
+        <v>4738</v>
       </c>
       <c r="D7" t="n">
-        <v>790</v>
+        <v>763</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>2506</v>
+        <v>1837</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>604</v>
+        <v>502</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2431</v>
+        <v>438</v>
       </c>
       <c r="C2" t="n">
-        <v>19364</v>
+        <v>10310</v>
       </c>
       <c r="D2" t="n">
-        <v>11509</v>
+        <v>8823</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1669</v>
+        <v>384</v>
       </c>
       <c r="C3" t="n">
-        <v>4658</v>
+        <v>5878</v>
       </c>
       <c r="D3" t="n">
-        <v>14058</v>
+        <v>10839</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1891</v>
+        <v>588</v>
       </c>
       <c r="C4" t="n">
-        <v>5646</v>
+        <v>3676</v>
       </c>
       <c r="D4" t="n">
-        <v>13108</v>
+        <v>11470</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1764</v>
+        <v>720</v>
       </c>
       <c r="C5" t="n">
-        <v>6488</v>
+        <v>5239</v>
       </c>
       <c r="D5" t="n">
-        <v>7580</v>
+        <v>7143</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1189</v>
+        <v>514</v>
       </c>
       <c r="C6" t="n">
-        <v>7272</v>
+        <v>6312</v>
       </c>
       <c r="D6" t="n">
-        <v>2899</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>408</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>6064</v>
+        <v>5627</v>
       </c>
       <c r="D7" t="n">
-        <v>966</v>
+        <v>988</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>3473</v>
+        <v>3087</v>
       </c>
       <c r="D8" t="n">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>1206</v>
+        <v>1051</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4171</v>
+        <v>3972</v>
       </c>
       <c r="C2" t="n">
-        <v>5479</v>
+        <v>11436</v>
       </c>
       <c r="D2" t="n">
-        <v>23136</v>
+        <v>7784</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1756</v>
+        <v>536</v>
       </c>
       <c r="C2" t="n">
-        <v>11308</v>
+        <v>25113</v>
       </c>
       <c r="D2" t="n">
-        <v>8562</v>
+        <v>12863</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2244</v>
+        <v>335</v>
       </c>
       <c r="C3" t="n">
-        <v>8251</v>
+        <v>6841</v>
       </c>
       <c r="D3" t="n">
-        <v>15021</v>
+        <v>9869</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2580</v>
+        <v>439</v>
       </c>
       <c r="C4" t="n">
-        <v>7940</v>
+        <v>4571</v>
       </c>
       <c r="D4" t="n">
-        <v>13522</v>
+        <v>11024</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1131</v>
+        <v>617</v>
       </c>
       <c r="C5" t="n">
-        <v>9883</v>
+        <v>4419</v>
       </c>
       <c r="D5" t="n">
-        <v>6906</v>
+        <v>7480</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>376</v>
+        <v>546</v>
       </c>
       <c r="C6" t="n">
-        <v>7296</v>
+        <v>5812</v>
       </c>
       <c r="D6" t="n">
-        <v>2215</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>287</v>
       </c>
       <c r="C7" t="n">
-        <v>3403</v>
+        <v>5844</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>1181</v>
+        <v>4081</v>
       </c>
       <c r="D8" t="n">
-        <v>286</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>317</v>
+        <v>1798</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>145</v>
+        <v>572</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5803</v>
+        <v>4521</v>
       </c>
       <c r="C2" t="n">
-        <v>8664</v>
+        <v>14354</v>
       </c>
       <c r="D2" t="n">
-        <v>34543</v>
+        <v>31676</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1774</v>
+        <v>1313</v>
       </c>
       <c r="C3" t="n">
-        <v>2761</v>
+        <v>4516</v>
       </c>
       <c r="D3" t="n">
-        <v>4526</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4618</v>
+        <v>2639</v>
       </c>
       <c r="C2" t="n">
-        <v>11249</v>
+        <v>9492</v>
       </c>
       <c r="D2" t="n">
-        <v>28087</v>
+        <v>27920</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3108</v>
+        <v>2467</v>
       </c>
       <c r="C3" t="n">
-        <v>5261</v>
+        <v>8909</v>
       </c>
       <c r="D3" t="n">
-        <v>9235</v>
+        <v>6835</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>805</v>
+        <v>633</v>
       </c>
       <c r="C4" t="n">
-        <v>1662</v>
+        <v>2823</v>
       </c>
       <c r="D4" t="n">
-        <v>2093</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5130</v>
+        <v>1868</v>
       </c>
       <c r="C2" t="n">
-        <v>10153</v>
+        <v>6928</v>
       </c>
       <c r="D2" t="n">
-        <v>31680</v>
+        <v>28667</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3187</v>
+        <v>2106</v>
       </c>
       <c r="C3" t="n">
-        <v>7340</v>
+        <v>7967</v>
       </c>
       <c r="D3" t="n">
-        <v>11586</v>
+        <v>9874</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1634</v>
+        <v>1347</v>
       </c>
       <c r="C4" t="n">
-        <v>3631</v>
+        <v>6328</v>
       </c>
       <c r="D4" t="n">
-        <v>3400</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="C5" t="n">
-        <v>990</v>
+        <v>1684</v>
       </c>
       <c r="D5" t="n">
-        <v>1313</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>370</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>343</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4897</v>
+        <v>2842</v>
       </c>
       <c r="C2" t="n">
-        <v>12227</v>
+        <v>6316</v>
       </c>
       <c r="D2" t="n">
-        <v>28942</v>
+        <v>24308</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3354</v>
+        <v>1650</v>
       </c>
       <c r="C3" t="n">
-        <v>7638</v>
+        <v>6426</v>
       </c>
       <c r="D3" t="n">
-        <v>13824</v>
+        <v>12169</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2028</v>
+        <v>1469</v>
       </c>
       <c r="C4" t="n">
-        <v>5513</v>
+        <v>7108</v>
       </c>
       <c r="D4" t="n">
-        <v>4789</v>
+        <v>3834</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>815</v>
+        <v>697</v>
       </c>
       <c r="C5" t="n">
-        <v>2303</v>
+        <v>4145</v>
       </c>
       <c r="D5" t="n">
-        <v>1621</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>231</v>
+        <v>188</v>
       </c>
       <c r="C6" t="n">
-        <v>644</v>
+        <v>996</v>
       </c>
       <c r="D6" t="n">
-        <v>965</v>
+        <v>818</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>372</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>340</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6024</v>
+        <v>3687</v>
       </c>
       <c r="C2" t="n">
-        <v>8494</v>
+        <v>4831</v>
       </c>
       <c r="D2" t="n">
-        <v>24528</v>
+        <v>38132</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2970</v>
+        <v>1796</v>
       </c>
       <c r="C3" t="n">
-        <v>8146</v>
+        <v>5566</v>
       </c>
       <c r="D3" t="n">
-        <v>14376</v>
+        <v>13079</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1646</v>
+        <v>1333</v>
       </c>
       <c r="C4" t="n">
-        <v>5451</v>
+        <v>6538</v>
       </c>
       <c r="D4" t="n">
-        <v>5365</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>733</v>
+        <v>924</v>
       </c>
       <c r="C5" t="n">
-        <v>2877</v>
+        <v>5566</v>
       </c>
       <c r="D5" t="n">
-        <v>1716</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>242</v>
+        <v>372</v>
       </c>
       <c r="C6" t="n">
-        <v>969</v>
+        <v>2527</v>
       </c>
       <c r="D6" t="n">
-        <v>807</v>
+        <v>879</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="C7" t="n">
-        <v>316</v>
+        <v>632</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>297</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>231</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4364</v>
+        <v>3800</v>
       </c>
       <c r="C2" t="n">
-        <v>5171</v>
+        <v>10831</v>
       </c>
       <c r="D2" t="n">
-        <v>21401</v>
+        <v>39061</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3697</v>
+        <v>2126</v>
       </c>
       <c r="C3" t="n">
-        <v>7194</v>
+        <v>4604</v>
       </c>
       <c r="D3" t="n">
-        <v>15023</v>
+        <v>15607</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1991</v>
+        <v>1312</v>
       </c>
       <c r="C4" t="n">
-        <v>6863</v>
+        <v>5872</v>
       </c>
       <c r="D4" t="n">
-        <v>7018</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1053</v>
+        <v>986</v>
       </c>
       <c r="C5" t="n">
-        <v>4299</v>
+        <v>5907</v>
       </c>
       <c r="D5" t="n">
-        <v>2347</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>445</v>
+        <v>546</v>
       </c>
       <c r="C6" t="n">
-        <v>2019</v>
+        <v>3848</v>
       </c>
       <c r="D6" t="n">
-        <v>970</v>
+        <v>994</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="C7" t="n">
-        <v>674</v>
+        <v>1486</v>
       </c>
       <c r="D7" t="n">
-        <v>571</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>270</v>
+        <v>441</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3719</v>
+        <v>3420</v>
       </c>
       <c r="C2" t="n">
-        <v>8096</v>
+        <v>6931</v>
       </c>
       <c r="D2" t="n">
-        <v>19170</v>
+        <v>31073</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3310</v>
+        <v>2548</v>
       </c>
       <c r="C3" t="n">
-        <v>5327</v>
+        <v>8294</v>
       </c>
       <c r="D3" t="n">
-        <v>14934</v>
+        <v>16947</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2396</v>
+        <v>911</v>
       </c>
       <c r="C4" t="n">
-        <v>6901</v>
+        <v>9165</v>
       </c>
       <c r="D4" t="n">
-        <v>8197</v>
+        <v>5663</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1325</v>
+        <v>504</v>
       </c>
       <c r="C5" t="n">
-        <v>5563</v>
+        <v>3771</v>
       </c>
       <c r="D5" t="n">
-        <v>3127</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>662</v>
+        <v>192</v>
       </c>
       <c r="C6" t="n">
-        <v>3137</v>
+        <v>1456</v>
       </c>
       <c r="D6" t="n">
-        <v>1194</v>
+        <v>630</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>1359</v>
+        <v>432</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>467</v>
+        <v>274</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
